--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484610_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484610_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5857</v>
+        <v>7.1329</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2151</v>
+        <v>10.6136</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.6294</v>
+        <v>-3.4807</v>
       </c>
       <c r="G2" t="n">
         <v>5.7601</v>
@@ -610,13 +610,13 @@
         <v>2.9321</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2765</v>
+        <v>-0.7292</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6252</v>
+        <v>-0.2266</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6513</v>
+        <v>-0.5027</v>
       </c>
       <c r="V2" t="n">
         <v>2.8351</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6428</v>
+        <v>2.2982</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0048</v>
+        <v>0.1234</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.362</v>
+        <v>2.1748</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.2543</v>
+        <v>1.6484</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4334</v>
+        <v>0.5073</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8209</v>
+        <v>1.1411</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5345</v>
+        <v>1.1786</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0089</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4743</v>
+        <v>0.6925</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.7888</v>
+        <v>0.4698</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4422</v>
+        <v>0.0213</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3466</v>
+        <v>0.4486</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3823</v>
+        <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5256</v>
+        <v>-0.6776</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1592</v>
+        <v>-0.4321</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3664</v>
+        <v>-0.2455</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8217</v>
+        <v>-0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1437</v>
+        <v>-0.6231</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3219</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.474</v>
+        <v>2.0465</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1506</v>
+        <v>3.6315</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3234</v>
+        <v>-1.585</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6484</v>
+        <v>-3.2543</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5073</v>
+        <v>-1.4334</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1411</v>
+        <v>-1.8209</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1786</v>
+        <v>0.5345</v>
       </c>
       <c r="K4" t="n">
-        <v>0.486</v>
+        <v>1.0089</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6925</v>
+        <v>-0.4743</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4698</v>
+        <v>-3.7888</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0213</v>
+        <v>-2.4422</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4486</v>
+        <v>-1.3466</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5018</v>
+        <v>0.9293</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.405</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0969</v>
+        <v>0.1435</v>
       </c>
       <c r="V4" t="n">
+        <v>3.8217</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.1437</v>
+      </c>
+      <c r="X4" t="n">
         <v>-0.3219</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.6231</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.3011</v>
       </c>
     </row>
     <row r="5">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1204</v>
+        <v>1.296</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1978</v>
+        <v>0.5964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9226</v>
+        <v>0.6996</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6526</v>
@@ -922,13 +922,13 @@
         <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5293</v>
+        <v>0.7049</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1086</v>
+        <v>0.5072</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4207</v>
+        <v>0.1978</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6816</v>
+        <v>-0.3325</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0621</v>
+        <v>-1.6635</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3805</v>
+        <v>1.331</v>
       </c>
       <c r="G7" t="n">
         <v>0.304</v>
@@ -1000,13 +1000,13 @@
         <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.619</v>
+        <v>-0.27</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4955</v>
+        <v>-0.0969</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1235</v>
+        <v>-0.1731</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DEL MORAL GALLARDO</t>
+          <t>R. TORREGROSA ROCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7282</v>
+        <v>-1.4729</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4509</v>
+        <v>-1.7616</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7227</v>
+        <v>0.2888</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-1.2815</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2461</v>
+        <v>0.2509</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3525</v>
+        <v>-1.5324</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8919</v>
+        <v>0.0117</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8919</v>
+        <v>0.486</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.4743</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0017</v>
+        <v>-1.2932</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3541</v>
+        <v>-0.2351</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3525</v>
+        <v>-1.0581</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3948</v>
+        <v>-0.2751</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0196</v>
+        <v>0.342</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3752</v>
+        <v>-0.6171</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6231</v>
+        <v>0.6335</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6231</v>
+        <v>0.6335</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>J. DEL MORAL GALLARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7789</v>
+        <v>-1.5904</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.694</v>
+        <v>-2.4369</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0849</v>
+        <v>0.8466</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0766</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1029</v>
+        <v>-1.2461</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1794</v>
+        <v>0.3525</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4835</v>
+        <v>-0.8919</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5668</v>
+        <v>-0.8919</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.0017</v>
       </c>
       <c r="N9" t="n">
-        <v>0.464</v>
+        <v>-0.3541</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0961</v>
+        <v>0.3525</v>
       </c>
       <c r="P9" t="n">
         <v>0.1833</v>
@@ -1156,28 +1156,28 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1486</v>
+        <v>-0.257</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3288</v>
+        <v>-0.0056</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4775</v>
+        <v>-0.2513</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.89</v>
+        <v>-0.6231</v>
       </c>
       <c r="W9" t="n">
         <v>-0.6231</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. TORREGROSA ROCA</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9402</v>
+        <v>-1.9875</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1052</v>
+        <v>-1.9274</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1649</v>
+        <v>-0.0601</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2815</v>
+        <v>0.0766</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2509</v>
+        <v>-0.1029</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5324</v>
+        <v>0.1794</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0117</v>
+        <v>-0.4835</v>
       </c>
       <c r="K10" t="n">
-        <v>0.486</v>
+        <v>-0.5668</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4743</v>
+        <v>0.0833</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2932</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2351</v>
+        <v>0.464</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0581</v>
+        <v>0.0961</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7425</v>
+        <v>-0.3573</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0015</v>
+        <v>0.0954</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.741</v>
+        <v>-0.4527</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6335</v>
+        <v>-1.89</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6335</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.98</v>
+        <v>-2.0296</v>
       </c>
       <c r="E11" t="n">
         <v>-0.928</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.052</v>
+        <v>-1.1016</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6069</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4727</v>
+        <v>-0.5222</v>
       </c>
       <c r="T11" t="n">
         <v>-0.3303</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1424</v>
+        <v>-0.1919</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3721</v>
+        <v>-3.0117</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7143</v>
+        <v>-2.453</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.5587</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2361</v>
@@ -1390,13 +1390,13 @@
         <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6858</v>
+        <v>-0.3254</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0565</v>
+        <v>0.2048</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6293</v>
+        <v>-0.5302</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.702</v>
+        <v>-3.8529</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7763</v>
+        <v>-0.952</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9257</v>
+        <v>-2.9009</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1116</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5958</v>
+        <v>-0.7468</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7526</v>
+        <v>0.0717</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8185</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2774</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6436</v>
+        <v>-6.3988</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.8991</v>
+        <v>-4.8029</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7445</v>
+        <v>-1.5959</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4252</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2026</v>
+        <v>-0.9578</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6606</v>
+        <v>-0.5645</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5419</v>
+        <v>-0.3933</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.4284</v>
+        <v>-6.327399999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.486300000000002</v>
+        <v>-0.3851000000000004</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.942200000000001</v>
+        <v>-5.942100000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-8.0974</v>
@@ -1594,16 +1594,16 @@
         <v>-7.9368</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1606999999999998</v>
+        <v>-0.1606999999999994</v>
       </c>
       <c r="J15" t="n">
-        <v>8.092599999999999</v>
+        <v>8.092600000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>3.923699999999999</v>
+        <v>3.9237</v>
       </c>
       <c r="L15" t="n">
-        <v>4.168899999999999</v>
+        <v>4.1689</v>
       </c>
       <c r="M15" t="n">
         <v>-16.1902</v>
@@ -1615,7 +1615,7 @@
         <v>-4.3296</v>
       </c>
       <c r="P15" t="n">
-        <v>3.665300000000001</v>
+        <v>3.6653</v>
       </c>
       <c r="Q15" t="n">
         <v>-16.4933</v>
@@ -1624,19 +1624,19 @@
         <v>20.1582</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.5852</v>
+        <v>-3.4842</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7502000000000004</v>
+        <v>0.3509000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.8351</v>
+        <v>-3.835</v>
       </c>
       <c r="V15" t="n">
         <v>1.589000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>7.664199999999999</v>
+        <v>7.6642</v>
       </c>
       <c r="X15" t="n">
         <v>-6.0753</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2404</v>
+        <v>5.2639</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4468</v>
+        <v>1.9022</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7937</v>
+        <v>3.3617</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.774</v>
+        <v>3.2228</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3702</v>
+        <v>1.8221</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5962</v>
+        <v>1.4007</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3209</v>
+        <v>2.73</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2052</v>
+        <v>1.9382</v>
       </c>
       <c r="L16" t="n">
-        <v>1.526</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0949</v>
+        <v>0.4928</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.165</v>
+        <v>-0.1161</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0.6089</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0158</v>
+        <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2918</v>
+        <v>-0.1867</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7202</v>
+        <v>-0.3722</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5716</v>
+        <v>0.1855</v>
       </c>
       <c r="V16" t="n">
-        <v>1.89</v>
+        <v>0.945</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5889</v>
+        <v>0.6439</v>
       </c>
       <c r="X16" t="n">
         <v>0.3011</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.0455</v>
+        <v>4.0078</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6138</v>
+        <v>2.5814</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4317</v>
+        <v>1.4264</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2228</v>
+        <v>-0.774</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8221</v>
+        <v>-1.3702</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4007</v>
+        <v>0.5962</v>
       </c>
       <c r="J17" t="n">
-        <v>2.73</v>
+        <v>0.3209</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9382</v>
+        <v>-1.2052</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7917999999999999</v>
+        <v>1.526</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4928</v>
+        <v>-1.0949</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1161</v>
+        <v>-0.165</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6089</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4051</v>
+        <v>1.0592</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6606</v>
+        <v>0.8548</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2555</v>
+        <v>0.2043</v>
       </c>
       <c r="V17" t="n">
-        <v>0.945</v>
+        <v>1.89</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6439</v>
+        <v>1.5889</v>
       </c>
       <c r="X17" t="n">
         <v>0.3011</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1651</v>
+        <v>2.2774</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7375</v>
+        <v>2.449</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5724</v>
+        <v>-0.1716</v>
       </c>
       <c r="G18" t="n">
         <v>2.8341</v>
@@ -1858,13 +1858,13 @@
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5144</v>
+        <v>-0.4022</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2006</v>
+        <v>-0.0878</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.715</v>
+        <v>-0.3143</v>
       </c>
       <c r="V18" t="n">
         <v>0.945</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5566</v>
+        <v>1.9294</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1926</v>
+        <v>2.395</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.636</v>
+        <v>-0.4656</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2141</v>
+        <v>2.6979</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8871</v>
+        <v>1.098</v>
       </c>
       <c r="I19" t="n">
-        <v>0.327</v>
+        <v>1.5998</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6051</v>
+        <v>4.055</v>
       </c>
       <c r="K19" t="n">
-        <v>2.22</v>
+        <v>1.4614</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3851</v>
+        <v>2.5937</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.391</v>
+        <v>-1.3572</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3329</v>
+        <v>-0.3633</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0581</v>
+        <v>-0.9938</v>
       </c>
       <c r="P19" t="n">
         <v>-0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0158</v>
+        <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4743</v>
+        <v>1.3049</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.7956</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0776</v>
+        <v>0.5092</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4646</v>
+        <v>1.8116</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2027</v>
+        <v>2.0964</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7381</v>
+        <v>-0.2848</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6979</v>
+        <v>2.2141</v>
       </c>
       <c r="H20" t="n">
-        <v>1.098</v>
+        <v>1.8871</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5998</v>
+        <v>0.327</v>
       </c>
       <c r="J20" t="n">
-        <v>4.055</v>
+        <v>3.6051</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4614</v>
+        <v>2.22</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5937</v>
+        <v>1.3851</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3572</v>
+        <v>-1.391</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3633</v>
+        <v>-0.3329</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9938</v>
+        <v>-1.0581</v>
       </c>
       <c r="P20" t="n">
         <v>-0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8401</v>
+        <v>-0.2193</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.5072</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2367</v>
+        <v>-0.7265</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3251</v>
+        <v>0.836</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3251</v>
+        <v>-1.6603</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.4962</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3251</v>
+        <v>-0.4238</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3251</v>
+        <v>1.0635</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-1.4872</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3251</v>
+        <v>-0.6693</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3251</v>
+        <v>1.1704</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.8397</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.2456</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.1069</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.4534</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.1086</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.3448</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="23">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2333</v>
+        <v>0.3251</v>
       </c>
       <c r="E24" t="n">
-        <v>2.062</v>
+        <v>0.3251</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2953</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1129</v>
+        <v>0.3251</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8361</v>
+        <v>0.3251</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.949</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.623</v>
+        <v>0.3251</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5139</v>
+        <v>0.3251</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7359</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6778</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0581</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3011</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8371</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3048</v>
+        <v>-1.7252</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4295</v>
+        <v>0.6197</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1246</v>
+        <v>-2.3448</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4238</v>
+        <v>-0.1129</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0635</v>
+        <v>0.8361</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4872</v>
+        <v>-0.949</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6693</v>
+        <v>1.623</v>
       </c>
       <c r="K25" t="n">
-        <v>1.1704</v>
+        <v>1.5139</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.8397</v>
+        <v>0.1091</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2456</v>
+        <v>-1.7359</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1069</v>
+        <v>-0.6778</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3525</v>
+        <v>-1.0581</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1833</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0995</v>
+        <v>-3.6651</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6874</v>
+        <v>1.8092</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6606</v>
+        <v>1.3948</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0268</v>
+        <v>0.4144</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6231</v>
+        <v>-1.5889</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X25" t="n">
-        <v>0.6231</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4279</v>
+        <v>-2.4353</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6299</v>
+        <v>-1.2453</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.798</v>
+        <v>-1.1901</v>
       </c>
       <c r="G26" t="n">
         <v>1.2225</v>
@@ -2482,13 +2482,13 @@
         <v>2.3823</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5724</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0927</v>
+        <v>0.2919</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6652</v>
+        <v>0.2732</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9242</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.0666</v>
+        <v>-2.7067</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.4923</v>
+        <v>-1.1077</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5743</v>
+        <v>-1.5991</v>
       </c>
       <c r="G27" t="n">
         <v>-2.0765</v>
@@ -2560,13 +2560,13 @@
         <v>0.5498</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2729</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2753</v>
+        <v>0.1094</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0023</v>
+        <v>-0.0224</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.9368</v>
+        <v>-3.115</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.6871</v>
+        <v>-4.014</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7503</v>
+        <v>0.8989</v>
       </c>
       <c r="G28" t="n">
         <v>-2.6325</v>
@@ -2638,13 +2638,13 @@
         <v>0.9163</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.7557</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.4404</v>
+        <v>0.2327</v>
       </c>
       <c r="U28" t="n">
-        <v>0.3744</v>
+        <v>0.523</v>
       </c>
       <c r="V28" t="n">
         <v>-0.3219</v>
@@ -2671,22 +2671,22 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>7.428299999999998</v>
+        <v>8.0694</v>
       </c>
       <c r="E29" t="n">
-        <v>5.942100000000001</v>
+        <v>5.941900000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4862</v>
+        <v>2.127199999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>8.097200000000001</v>
+        <v>8.097200000000003</v>
       </c>
       <c r="H29" t="n">
         <v>7.9368</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1606000000000001</v>
+        <v>0.1606000000000005</v>
       </c>
       <c r="J29" t="n">
         <v>16.19</v>
@@ -2695,7 +2695,7 @@
         <v>11.8604</v>
       </c>
       <c r="L29" t="n">
-        <v>4.3296</v>
+        <v>4.329600000000001</v>
       </c>
       <c r="M29" t="n">
         <v>-8.092700000000001</v>
@@ -2716,13 +2716,13 @@
         <v>16.4931</v>
       </c>
       <c r="S29" t="n">
-        <v>4.585199999999999</v>
+        <v>5.2261</v>
       </c>
       <c r="T29" t="n">
-        <v>3.834900000000002</v>
+        <v>3.835</v>
       </c>
       <c r="U29" t="n">
-        <v>0.7502000000000002</v>
+        <v>1.3912</v>
       </c>
       <c r="V29" t="n">
         <v>-1.5889</v>
